--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\script\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{455B6EEC-A91E-4D70-90FA-FAD8D6D94FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31328A28-8CC3-4F08-A3BF-8BFA0A5AFDD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="42">
   <si>
     <t>Symbol</t>
   </si>
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
@@ -1274,6 +1274,152 @@
         <v>46204</v>
       </c>
     </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>27</v>
+      </c>
+      <c r="B41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41">
+        <v>500</v>
+      </c>
+      <c r="D41">
+        <v>19.7</v>
+      </c>
+      <c r="E41">
+        <v>0.74</v>
+      </c>
+      <c r="F41" s="2">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>22</v>
+      </c>
+      <c r="B42" t="s">
+        <v>26</v>
+      </c>
+      <c r="C42">
+        <v>115.2</v>
+      </c>
+      <c r="F42" s="2">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43" t="s">
+        <v>26</v>
+      </c>
+      <c r="C43">
+        <v>169.5</v>
+      </c>
+      <c r="F43" s="2">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>22</v>
+      </c>
+      <c r="B44" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44">
+        <v>126</v>
+      </c>
+      <c r="F44" s="2">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>22</v>
+      </c>
+      <c r="B45" t="s">
+        <v>26</v>
+      </c>
+      <c r="C45">
+        <v>170</v>
+      </c>
+      <c r="F45" s="2">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>22</v>
+      </c>
+      <c r="B46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46">
+        <v>64.8</v>
+      </c>
+      <c r="F46" s="2">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>22</v>
+      </c>
+      <c r="B47" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47">
+        <v>585</v>
+      </c>
+      <c r="F47" s="2">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>22</v>
+      </c>
+      <c r="B48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48">
+        <v>54</v>
+      </c>
+      <c r="F48" s="2">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>22</v>
+      </c>
+      <c r="B49" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49">
+        <v>189</v>
+      </c>
+      <c r="F49" s="2">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50" t="s">
+        <v>26</v>
+      </c>
+      <c r="C50">
+        <v>160.38</v>
+      </c>
+      <c r="F50" s="2">
+        <v>46290</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\script\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31328A28-8CC3-4F08-A3BF-8BFA0A5AFDD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172C3FE4-16C9-42FB-A200-8248E06021D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="42">
   <si>
     <t>Symbol</t>
   </si>
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
@@ -1420,6 +1420,20 @@
         <v>46290</v>
       </c>
     </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>13</v>
+      </c>
+      <c r="B51" t="s">
+        <v>26</v>
+      </c>
+      <c r="C51">
+        <v>1008</v>
+      </c>
+      <c r="F51" s="2">
+        <v>46317</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
